--- a/v1.2/A2PICO2.v1.2_CPL.xlsx
+++ b/v1.2/A2PICO2.v1.2_CPL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ralle\Documents\A2PICO2.v1.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A59C84C-9049-4831-8B36-877D69355AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C65E911B-51DC-49A5-9486-29B65BFE560A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -675,7 +675,7 @@
         <v>5</v>
       </c>
       <c r="E3" s="4">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
@@ -725,7 +725,7 @@
         <v>5</v>
       </c>
       <c r="E5" s="4">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
@@ -750,7 +750,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="4">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -850,7 +850,7 @@
         <v>5</v>
       </c>
       <c r="E10" s="4">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
@@ -875,7 +875,7 @@
         <v>5</v>
       </c>
       <c r="E11" s="4">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
@@ -925,7 +925,7 @@
         <v>5</v>
       </c>
       <c r="E13" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
@@ -950,7 +950,7 @@
         <v>5</v>
       </c>
       <c r="E14" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
@@ -975,7 +975,7 @@
         <v>5</v>
       </c>
       <c r="E15" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
@@ -1125,7 +1125,7 @@
         <v>5</v>
       </c>
       <c r="E21" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
@@ -1200,7 +1200,7 @@
         <v>5</v>
       </c>
       <c r="E24" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
@@ -1375,7 +1375,7 @@
         <v>5</v>
       </c>
       <c r="E31" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
@@ -1473,7 +1473,7 @@
         <v>5</v>
       </c>
       <c r="E35" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
@@ -1497,7 +1497,7 @@
         <v>5</v>
       </c>
       <c r="E36" s="4">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
@@ -1521,7 +1521,7 @@
         <v>5</v>
       </c>
       <c r="E37" s="4">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
@@ -1857,7 +1857,7 @@
         <v>5</v>
       </c>
       <c r="E51" s="4">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
